--- a/zy72118/data/laser_calibration_sample.xlsx
+++ b/zy72118/data/laser_calibration_sample.xlsx
@@ -40,13 +40,13 @@
     <t>操作人员</t>
   </si>
   <si>
-    <t>正向</t>
+    <t>CW</t>
   </si>
   <si>
-    <t>反向</t>
+    <t>CCW</t>
   </si>
   <si>
-    <t>未知</t>
+    <t>UNKNOWN</t>
   </si>
   <si>
     <t>LASER-001</t>
